--- a/f2_tabelas/tabela_prematuridade_por_ano.xlsx
+++ b/f2_tabelas/tabela_prematuridade_por_ano.xlsx
@@ -19,6 +19,7 @@
     <sheet name="2021" sheetId="10" r:id="rId10"/>
     <sheet name="2022" sheetId="11" r:id="rId11"/>
     <sheet name="2023" sheetId="12" r:id="rId12"/>
+    <sheet name="2024" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11960,6 +11961,2906 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nascidos vivos</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Partos prematuros</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pindicado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P prematuro Indicado "Prematuro moderado" 32 a 37 semanas</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P prematuro Indicado "Muito prematuro" 28 semanas a 31+6d</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P prematuro Indicado "Extremamente prematuro" &lt; 28 semanas</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Pespontâneo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P prematuro espontâneo "tardio" 32 a 37 semanas</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P prematuro espontâneo "Muito prematuro" 28 semanas a 31+6d</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P prematuro espontâneo "Extremamente prematuro" &lt; 28 semanas</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Partos termos precoces (37+1 - 38+6)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Partos termos precoces Indicados (37+1 - 38+6)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Partos termos precoces espontâneos (37+1 - 38+6)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Partos termo (controle) &gt; 37 +1 d</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raça</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Branca</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>242140</v>
+      </c>
+      <c r="D2">
+        <v>29479</v>
+      </c>
+      <c r="E2">
+        <v>16583</v>
+      </c>
+      <c r="F2">
+        <v>14736</v>
+      </c>
+      <c r="G2">
+        <v>1335</v>
+      </c>
+      <c r="H2">
+        <v>512</v>
+      </c>
+      <c r="I2">
+        <v>6240</v>
+      </c>
+      <c r="J2">
+        <v>5432</v>
+      </c>
+      <c r="K2">
+        <v>554</v>
+      </c>
+      <c r="L2">
+        <v>254</v>
+      </c>
+      <c r="M2">
+        <v>92197</v>
+      </c>
+      <c r="N2">
+        <v>57659</v>
+      </c>
+      <c r="O2">
+        <v>16433</v>
+      </c>
+      <c r="P2">
+        <v>212411</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Raça</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Preta</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>38326</v>
+      </c>
+      <c r="D3">
+        <v>4929</v>
+      </c>
+      <c r="E3">
+        <v>2764</v>
+      </c>
+      <c r="F3">
+        <v>2435</v>
+      </c>
+      <c r="G3">
+        <v>241</v>
+      </c>
+      <c r="H3">
+        <v>88</v>
+      </c>
+      <c r="I3">
+        <v>766</v>
+      </c>
+      <c r="J3">
+        <v>639</v>
+      </c>
+      <c r="K3">
+        <v>84</v>
+      </c>
+      <c r="L3">
+        <v>43</v>
+      </c>
+      <c r="M3">
+        <v>12923</v>
+      </c>
+      <c r="N3">
+        <v>7835</v>
+      </c>
+      <c r="O3">
+        <v>1590</v>
+      </c>
+      <c r="P3">
+        <v>33347</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Raça</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Parda</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>182983</v>
+      </c>
+      <c r="D4">
+        <v>22610</v>
+      </c>
+      <c r="E4">
+        <v>12242</v>
+      </c>
+      <c r="F4">
+        <v>10875</v>
+      </c>
+      <c r="G4">
+        <v>977</v>
+      </c>
+      <c r="H4">
+        <v>390</v>
+      </c>
+      <c r="I4">
+        <v>3572</v>
+      </c>
+      <c r="J4">
+        <v>2965</v>
+      </c>
+      <c r="K4">
+        <v>431</v>
+      </c>
+      <c r="L4">
+        <v>176</v>
+      </c>
+      <c r="M4">
+        <v>62586</v>
+      </c>
+      <c r="N4">
+        <v>37047</v>
+      </c>
+      <c r="O4">
+        <v>8009</v>
+      </c>
+      <c r="P4">
+        <v>160188</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Raça</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amarela</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>2561</v>
+      </c>
+      <c r="D5">
+        <v>323</v>
+      </c>
+      <c r="E5">
+        <v>171</v>
+      </c>
+      <c r="F5">
+        <v>161</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>73</v>
+      </c>
+      <c r="J5">
+        <v>61</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1008</v>
+      </c>
+      <c r="N5">
+        <v>624</v>
+      </c>
+      <c r="O5">
+        <v>160</v>
+      </c>
+      <c r="P5">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Raça</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Indígena</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>485</v>
+      </c>
+      <c r="D6">
+        <v>66</v>
+      </c>
+      <c r="E6">
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>181</v>
+      </c>
+      <c r="N6">
+        <v>78</v>
+      </c>
+      <c r="O6">
+        <v>16</v>
+      </c>
+      <c r="P6">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Raça</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>4132</v>
+      </c>
+      <c r="D7">
+        <v>277</v>
+      </c>
+      <c r="E7">
+        <v>72</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>397</v>
+      </c>
+      <c r="N7">
+        <v>233</v>
+      </c>
+      <c r="O7">
+        <v>74</v>
+      </c>
+      <c r="P7">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sem escolaridade</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>244</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>18</v>
+      </c>
+      <c r="F9">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>87</v>
+      </c>
+      <c r="N9">
+        <v>41</v>
+      </c>
+      <c r="O9">
+        <v>16</v>
+      </c>
+      <c r="P9">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fundamental I</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3624</v>
+      </c>
+      <c r="D10">
+        <v>560</v>
+      </c>
+      <c r="E10">
+        <v>274</v>
+      </c>
+      <c r="F10">
+        <v>249</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>95</v>
+      </c>
+      <c r="J10">
+        <v>81</v>
+      </c>
+      <c r="K10">
+        <v>13</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1297</v>
+      </c>
+      <c r="N10">
+        <v>722</v>
+      </c>
+      <c r="O10">
+        <v>146</v>
+      </c>
+      <c r="P10">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fundamental II</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>46239</v>
+      </c>
+      <c r="D11">
+        <v>6773</v>
+      </c>
+      <c r="E11">
+        <v>3319</v>
+      </c>
+      <c r="F11">
+        <v>2917</v>
+      </c>
+      <c r="G11">
+        <v>289</v>
+      </c>
+      <c r="H11">
+        <v>113</v>
+      </c>
+      <c r="I11">
+        <v>1081</v>
+      </c>
+      <c r="J11">
+        <v>897</v>
+      </c>
+      <c r="K11">
+        <v>135</v>
+      </c>
+      <c r="L11">
+        <v>49</v>
+      </c>
+      <c r="M11">
+        <v>15636</v>
+      </c>
+      <c r="N11">
+        <v>8318</v>
+      </c>
+      <c r="O11">
+        <v>1954</v>
+      </c>
+      <c r="P11">
+        <v>39376</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>276471</v>
+      </c>
+      <c r="D12">
+        <v>33469</v>
+      </c>
+      <c r="E12">
+        <v>18210</v>
+      </c>
+      <c r="F12">
+        <v>16175</v>
+      </c>
+      <c r="G12">
+        <v>1476</v>
+      </c>
+      <c r="H12">
+        <v>559</v>
+      </c>
+      <c r="I12">
+        <v>5499</v>
+      </c>
+      <c r="J12">
+        <v>4674</v>
+      </c>
+      <c r="K12">
+        <v>556</v>
+      </c>
+      <c r="L12">
+        <v>269</v>
+      </c>
+      <c r="M12">
+        <v>95237</v>
+      </c>
+      <c r="N12">
+        <v>56678</v>
+      </c>
+      <c r="O12">
+        <v>13317</v>
+      </c>
+      <c r="P12">
+        <v>242709</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Superior incompleto</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>23664</v>
+      </c>
+      <c r="D13">
+        <v>2791</v>
+      </c>
+      <c r="E13">
+        <v>1684</v>
+      </c>
+      <c r="F13">
+        <v>1491</v>
+      </c>
+      <c r="G13">
+        <v>142</v>
+      </c>
+      <c r="H13">
+        <v>51</v>
+      </c>
+      <c r="I13">
+        <v>561</v>
+      </c>
+      <c r="J13">
+        <v>466</v>
+      </c>
+      <c r="K13">
+        <v>65</v>
+      </c>
+      <c r="L13">
+        <v>30</v>
+      </c>
+      <c r="M13">
+        <v>8963</v>
+      </c>
+      <c r="N13">
+        <v>5877</v>
+      </c>
+      <c r="O13">
+        <v>1407</v>
+      </c>
+      <c r="P13">
+        <v>20855</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Superior completo</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>116918</v>
+      </c>
+      <c r="D14">
+        <v>13838</v>
+      </c>
+      <c r="E14">
+        <v>8319</v>
+      </c>
+      <c r="F14">
+        <v>7415</v>
+      </c>
+      <c r="G14">
+        <v>645</v>
+      </c>
+      <c r="H14">
+        <v>259</v>
+      </c>
+      <c r="I14">
+        <v>3435</v>
+      </c>
+      <c r="J14">
+        <v>3001</v>
+      </c>
+      <c r="K14">
+        <v>306</v>
+      </c>
+      <c r="L14">
+        <v>128</v>
+      </c>
+      <c r="M14">
+        <v>47926</v>
+      </c>
+      <c r="N14">
+        <v>31755</v>
+      </c>
+      <c r="O14">
+        <v>9426</v>
+      </c>
+      <c r="P14">
+        <v>102996</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ignorado</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>248</v>
+      </c>
+      <c r="D15">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <v>28</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>81</v>
+      </c>
+      <c r="N15">
+        <v>47</v>
+      </c>
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="P15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Escolaridade</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>3219</v>
+      </c>
+      <c r="D16">
+        <v>163</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>65</v>
+      </c>
+      <c r="N16">
+        <v>38</v>
+      </c>
+      <c r="O16">
+        <v>6</v>
+      </c>
+      <c r="P16">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Situação conjugal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Solteira/Viúva/divorciada</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>225552</v>
+      </c>
+      <c r="D18">
+        <v>28408</v>
+      </c>
+      <c r="E18">
+        <v>14940</v>
+      </c>
+      <c r="F18">
+        <v>13169</v>
+      </c>
+      <c r="G18">
+        <v>1289</v>
+      </c>
+      <c r="H18">
+        <v>482</v>
+      </c>
+      <c r="I18">
+        <v>4530</v>
+      </c>
+      <c r="J18">
+        <v>3779</v>
+      </c>
+      <c r="K18">
+        <v>502</v>
+      </c>
+      <c r="L18">
+        <v>249</v>
+      </c>
+      <c r="M18">
+        <v>75771</v>
+      </c>
+      <c r="N18">
+        <v>44301</v>
+      </c>
+      <c r="O18">
+        <v>9875</v>
+      </c>
+      <c r="P18">
+        <v>196879</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Situação conjugal</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Casada/União estável</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>243976</v>
+      </c>
+      <c r="D19">
+        <v>29116</v>
+      </c>
+      <c r="E19">
+        <v>16853</v>
+      </c>
+      <c r="F19">
+        <v>15068</v>
+      </c>
+      <c r="G19">
+        <v>1274</v>
+      </c>
+      <c r="H19">
+        <v>511</v>
+      </c>
+      <c r="I19">
+        <v>6116</v>
+      </c>
+      <c r="J19">
+        <v>5317</v>
+      </c>
+      <c r="K19">
+        <v>572</v>
+      </c>
+      <c r="L19">
+        <v>227</v>
+      </c>
+      <c r="M19">
+        <v>93121</v>
+      </c>
+      <c r="N19">
+        <v>58941</v>
+      </c>
+      <c r="O19">
+        <v>16338</v>
+      </c>
+      <c r="P19">
+        <v>214619</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Situação conjugal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ignorado</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>518</v>
+      </c>
+      <c r="D20">
+        <v>80</v>
+      </c>
+      <c r="E20">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>25</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>20</v>
+      </c>
+      <c r="J20">
+        <v>18</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>180</v>
+      </c>
+      <c r="N20">
+        <v>101</v>
+      </c>
+      <c r="O20">
+        <v>24</v>
+      </c>
+      <c r="P20">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Situação conjugal</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>581</v>
+      </c>
+      <c r="D21">
+        <v>80</v>
+      </c>
+      <c r="E21">
+        <v>40</v>
+      </c>
+      <c r="F21">
+        <v>37</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>17</v>
+      </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>220</v>
+      </c>
+      <c r="N21">
+        <v>133</v>
+      </c>
+      <c r="O21">
+        <v>45</v>
+      </c>
+      <c r="P21">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>125071</v>
+      </c>
+      <c r="D23">
+        <v>15215</v>
+      </c>
+      <c r="E23">
+        <v>8722</v>
+      </c>
+      <c r="F23">
+        <v>7765</v>
+      </c>
+      <c r="G23">
+        <v>664</v>
+      </c>
+      <c r="H23">
+        <v>293</v>
+      </c>
+      <c r="I23">
+        <v>3193</v>
+      </c>
+      <c r="J23">
+        <v>2749</v>
+      </c>
+      <c r="K23">
+        <v>318</v>
+      </c>
+      <c r="L23">
+        <v>126</v>
+      </c>
+      <c r="M23">
+        <v>47178</v>
+      </c>
+      <c r="N23">
+        <v>29460</v>
+      </c>
+      <c r="O23">
+        <v>8396</v>
+      </c>
+      <c r="P23">
+        <v>109777</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>220980</v>
+      </c>
+      <c r="D24">
+        <v>25869</v>
+      </c>
+      <c r="E24">
+        <v>14647</v>
+      </c>
+      <c r="F24">
+        <v>13098</v>
+      </c>
+      <c r="G24">
+        <v>1149</v>
+      </c>
+      <c r="H24">
+        <v>400</v>
+      </c>
+      <c r="I24">
+        <v>4860</v>
+      </c>
+      <c r="J24">
+        <v>4155</v>
+      </c>
+      <c r="K24">
+        <v>478</v>
+      </c>
+      <c r="L24">
+        <v>227</v>
+      </c>
+      <c r="M24">
+        <v>80801</v>
+      </c>
+      <c r="N24">
+        <v>50213</v>
+      </c>
+      <c r="O24">
+        <v>12307</v>
+      </c>
+      <c r="P24">
+        <v>194962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>67420</v>
+      </c>
+      <c r="D25">
+        <v>8361</v>
+      </c>
+      <c r="E25">
+        <v>4617</v>
+      </c>
+      <c r="F25">
+        <v>4089</v>
+      </c>
+      <c r="G25">
+        <v>374</v>
+      </c>
+      <c r="H25">
+        <v>154</v>
+      </c>
+      <c r="I25">
+        <v>1430</v>
+      </c>
+      <c r="J25">
+        <v>1239</v>
+      </c>
+      <c r="K25">
+        <v>137</v>
+      </c>
+      <c r="L25">
+        <v>54</v>
+      </c>
+      <c r="M25">
+        <v>23391</v>
+      </c>
+      <c r="N25">
+        <v>14221</v>
+      </c>
+      <c r="O25">
+        <v>3315</v>
+      </c>
+      <c r="P25">
+        <v>59014</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>23056</v>
+      </c>
+      <c r="D26">
+        <v>3046</v>
+      </c>
+      <c r="E26">
+        <v>1620</v>
+      </c>
+      <c r="F26">
+        <v>1407</v>
+      </c>
+      <c r="G26">
+        <v>157</v>
+      </c>
+      <c r="H26">
+        <v>56</v>
+      </c>
+      <c r="I26">
+        <v>494</v>
+      </c>
+      <c r="J26">
+        <v>419</v>
+      </c>
+      <c r="K26">
+        <v>47</v>
+      </c>
+      <c r="L26">
+        <v>28</v>
+      </c>
+      <c r="M26">
+        <v>7698</v>
+      </c>
+      <c r="N26">
+        <v>4493</v>
+      </c>
+      <c r="O26">
+        <v>984</v>
+      </c>
+      <c r="P26">
+        <v>19981</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>12129</v>
+      </c>
+      <c r="D27">
+        <v>1848</v>
+      </c>
+      <c r="E27">
+        <v>914</v>
+      </c>
+      <c r="F27">
+        <v>798</v>
+      </c>
+      <c r="G27">
+        <v>84</v>
+      </c>
+      <c r="H27">
+        <v>32</v>
+      </c>
+      <c r="I27">
+        <v>267</v>
+      </c>
+      <c r="J27">
+        <v>210</v>
+      </c>
+      <c r="K27">
+        <v>42</v>
+      </c>
+      <c r="L27">
+        <v>15</v>
+      </c>
+      <c r="M27">
+        <v>3910</v>
+      </c>
+      <c r="N27">
+        <v>2116</v>
+      </c>
+      <c r="O27">
+        <v>505</v>
+      </c>
+      <c r="P27">
+        <v>10272</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>6420</v>
+      </c>
+      <c r="D28">
+        <v>936</v>
+      </c>
+      <c r="E28">
+        <v>450</v>
+      </c>
+      <c r="F28">
+        <v>386</v>
+      </c>
+      <c r="G28">
+        <v>49</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28">
+        <v>138</v>
+      </c>
+      <c r="J28">
+        <v>114</v>
+      </c>
+      <c r="K28">
+        <v>17</v>
+      </c>
+      <c r="L28">
+        <v>7</v>
+      </c>
+      <c r="M28">
+        <v>2136</v>
+      </c>
+      <c r="N28">
+        <v>1064</v>
+      </c>
+      <c r="O28">
+        <v>279</v>
+      </c>
+      <c r="P28">
+        <v>5469</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>3572</v>
+      </c>
+      <c r="D29">
+        <v>517</v>
+      </c>
+      <c r="E29">
+        <v>242</v>
+      </c>
+      <c r="F29">
+        <v>211</v>
+      </c>
+      <c r="G29">
+        <v>29</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>58</v>
+      </c>
+      <c r="J29">
+        <v>50</v>
+      </c>
+      <c r="K29">
+        <v>7</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>1200</v>
+      </c>
+      <c r="N29">
+        <v>630</v>
+      </c>
+      <c r="O29">
+        <v>153</v>
+      </c>
+      <c r="P29">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>2174</v>
+      </c>
+      <c r="D30">
+        <v>302</v>
+      </c>
+      <c r="E30">
+        <v>133</v>
+      </c>
+      <c r="F30">
+        <v>129</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>47</v>
+      </c>
+      <c r="J30">
+        <v>43</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>751</v>
+      </c>
+      <c r="N30">
+        <v>352</v>
+      </c>
+      <c r="O30">
+        <v>97</v>
+      </c>
+      <c r="P30">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>786</v>
+      </c>
+      <c r="D31">
+        <v>61</v>
+      </c>
+      <c r="E31">
+        <v>28</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>11</v>
+      </c>
+      <c r="J31">
+        <v>11</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>284</v>
+      </c>
+      <c r="N31">
+        <v>139</v>
+      </c>
+      <c r="O31">
+        <v>34</v>
+      </c>
+      <c r="P31">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>3087</v>
+      </c>
+      <c r="D32">
+        <v>756</v>
+      </c>
+      <c r="E32">
+        <v>295</v>
+      </c>
+      <c r="F32">
+        <v>239</v>
+      </c>
+      <c r="G32">
+        <v>33</v>
+      </c>
+      <c r="H32">
+        <v>23</v>
+      </c>
+      <c r="I32">
+        <v>108</v>
+      </c>
+      <c r="J32">
+        <v>81</v>
+      </c>
+      <c r="K32">
+        <v>19</v>
+      </c>
+      <c r="L32">
+        <v>8</v>
+      </c>
+      <c r="M32">
+        <v>977</v>
+      </c>
+      <c r="N32">
+        <v>419</v>
+      </c>
+      <c r="O32">
+        <v>123</v>
+      </c>
+      <c r="P32">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mês do pré-natal</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>5932</v>
+      </c>
+      <c r="D33">
+        <v>773</v>
+      </c>
+      <c r="E33">
+        <v>196</v>
+      </c>
+      <c r="F33">
+        <v>149</v>
+      </c>
+      <c r="G33">
+        <v>27</v>
+      </c>
+      <c r="H33">
+        <v>20</v>
+      </c>
+      <c r="I33">
+        <v>77</v>
+      </c>
+      <c r="J33">
+        <v>56</v>
+      </c>
+      <c r="K33">
+        <v>10</v>
+      </c>
+      <c r="L33">
+        <v>11</v>
+      </c>
+      <c r="M33">
+        <v>966</v>
+      </c>
+      <c r="N33">
+        <v>369</v>
+      </c>
+      <c r="O33">
+        <v>89</v>
+      </c>
+      <c r="P33">
+        <v>5075</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tipo de gravidez</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>458276</v>
+      </c>
+      <c r="D35">
+        <v>49317</v>
+      </c>
+      <c r="E35">
+        <v>26722</v>
+      </c>
+      <c r="F35">
+        <v>23736</v>
+      </c>
+      <c r="G35">
+        <v>2144</v>
+      </c>
+      <c r="H35">
+        <v>842</v>
+      </c>
+      <c r="I35">
+        <v>8258</v>
+      </c>
+      <c r="J35">
+        <v>7202</v>
+      </c>
+      <c r="K35">
+        <v>726</v>
+      </c>
+      <c r="L35">
+        <v>330</v>
+      </c>
+      <c r="M35">
+        <v>165781</v>
+      </c>
+      <c r="N35">
+        <v>100816</v>
+      </c>
+      <c r="O35">
+        <v>25613</v>
+      </c>
+      <c r="P35">
+        <v>408472</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tipo de gravidez</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Dupla</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>12035</v>
+      </c>
+      <c r="D36">
+        <v>8154</v>
+      </c>
+      <c r="E36">
+        <v>5028</v>
+      </c>
+      <c r="F36">
+        <v>4480</v>
+      </c>
+      <c r="G36">
+        <v>398</v>
+      </c>
+      <c r="H36">
+        <v>150</v>
+      </c>
+      <c r="I36">
+        <v>2346</v>
+      </c>
+      <c r="J36">
+        <v>1888</v>
+      </c>
+      <c r="K36">
+        <v>328</v>
+      </c>
+      <c r="L36">
+        <v>130</v>
+      </c>
+      <c r="M36">
+        <v>3469</v>
+      </c>
+      <c r="N36">
+        <v>2642</v>
+      </c>
+      <c r="O36">
+        <v>664</v>
+      </c>
+      <c r="P36">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tipo de gravidez</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ignorado</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>11</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tipo de gravidez</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>102</v>
+      </c>
+      <c r="D38">
+        <v>16</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>31</v>
+      </c>
+      <c r="N38">
+        <v>13</v>
+      </c>
+      <c r="O38">
+        <v>4</v>
+      </c>
+      <c r="P38">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tipo de gravidez</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>203</v>
+      </c>
+      <c r="D39">
+        <v>196</v>
+      </c>
+      <c r="E39">
+        <v>109</v>
+      </c>
+      <c r="F39">
+        <v>79</v>
+      </c>
+      <c r="G39">
+        <v>27</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>78</v>
+      </c>
+      <c r="J39">
+        <v>36</v>
+      </c>
+      <c r="K39">
+        <v>25</v>
+      </c>
+      <c r="L39">
+        <v>17</v>
+      </c>
+      <c r="M39">
+        <v>7</v>
+      </c>
+      <c r="N39">
+        <v>5</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Adequação do pré-natal</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Adequado</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>401615</v>
+      </c>
+      <c r="D41">
+        <v>50494</v>
+      </c>
+      <c r="E41">
+        <v>28768</v>
+      </c>
+      <c r="F41">
+        <v>25550</v>
+      </c>
+      <c r="G41">
+        <v>2304</v>
+      </c>
+      <c r="H41">
+        <v>914</v>
+      </c>
+      <c r="I41">
+        <v>9659</v>
+      </c>
+      <c r="J41">
+        <v>8248</v>
+      </c>
+      <c r="K41">
+        <v>974</v>
+      </c>
+      <c r="L41">
+        <v>437</v>
+      </c>
+      <c r="M41">
+        <v>148177</v>
+      </c>
+      <c r="N41">
+        <v>92793</v>
+      </c>
+      <c r="O41">
+        <v>23354</v>
+      </c>
+      <c r="P41">
+        <v>351121</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Adequação do pré-natal</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inadequado</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>64667</v>
+      </c>
+      <c r="D42">
+        <v>6913</v>
+      </c>
+      <c r="E42">
+        <v>3041</v>
+      </c>
+      <c r="F42">
+        <v>2706</v>
+      </c>
+      <c r="G42">
+        <v>260</v>
+      </c>
+      <c r="H42">
+        <v>75</v>
+      </c>
+      <c r="I42">
+        <v>1007</v>
+      </c>
+      <c r="J42">
+        <v>864</v>
+      </c>
+      <c r="K42">
+        <v>105</v>
+      </c>
+      <c r="L42">
+        <v>38</v>
+      </c>
+      <c r="M42">
+        <v>20824</v>
+      </c>
+      <c r="N42">
+        <v>10550</v>
+      </c>
+      <c r="O42">
+        <v>2884</v>
+      </c>
+      <c r="P42">
+        <v>57754</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Adequação do pré-natal</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>4345</v>
+      </c>
+      <c r="D43">
+        <v>277</v>
+      </c>
+      <c r="E43">
+        <v>55</v>
+      </c>
+      <c r="F43">
+        <v>43</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="H43">
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>17</v>
+      </c>
+      <c r="J43">
+        <v>15</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>291</v>
+      </c>
+      <c r="N43">
+        <v>133</v>
+      </c>
+      <c r="O43">
+        <v>44</v>
+      </c>
+      <c r="P43">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Número de cesáreas anteriores</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>325469</v>
+      </c>
+      <c r="D45">
+        <v>39965</v>
+      </c>
+      <c r="E45">
+        <v>20526</v>
+      </c>
+      <c r="F45">
+        <v>18079</v>
+      </c>
+      <c r="G45">
+        <v>1740</v>
+      </c>
+      <c r="H45">
+        <v>707</v>
+      </c>
+      <c r="I45">
+        <v>6643</v>
+      </c>
+      <c r="J45">
+        <v>5554</v>
+      </c>
+      <c r="K45">
+        <v>728</v>
+      </c>
+      <c r="L45">
+        <v>361</v>
+      </c>
+      <c r="M45">
+        <v>110934</v>
+      </c>
+      <c r="N45">
+        <v>62254</v>
+      </c>
+      <c r="O45">
+        <v>14653</v>
+      </c>
+      <c r="P45">
+        <v>285199</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Número de cesáreas anteriores</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>103439</v>
+      </c>
+      <c r="D46">
+        <v>11958</v>
+      </c>
+      <c r="E46">
+        <v>7465</v>
+      </c>
+      <c r="F46">
+        <v>6700</v>
+      </c>
+      <c r="G46">
+        <v>580</v>
+      </c>
+      <c r="H46">
+        <v>185</v>
+      </c>
+      <c r="I46">
+        <v>2592</v>
+      </c>
+      <c r="J46">
+        <v>2301</v>
+      </c>
+      <c r="K46">
+        <v>220</v>
+      </c>
+      <c r="L46">
+        <v>71</v>
+      </c>
+      <c r="M46">
+        <v>41015</v>
+      </c>
+      <c r="N46">
+        <v>28144</v>
+      </c>
+      <c r="O46">
+        <v>7948</v>
+      </c>
+      <c r="P46">
+        <v>91351</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Número de cesáreas anteriores</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2 ou mais</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>37804</v>
+      </c>
+      <c r="D47">
+        <v>5496</v>
+      </c>
+      <c r="E47">
+        <v>3811</v>
+      </c>
+      <c r="F47">
+        <v>3467</v>
+      </c>
+      <c r="G47">
+        <v>244</v>
+      </c>
+      <c r="H47">
+        <v>100</v>
+      </c>
+      <c r="I47">
+        <v>1433</v>
+      </c>
+      <c r="J47">
+        <v>1259</v>
+      </c>
+      <c r="K47">
+        <v>129</v>
+      </c>
+      <c r="L47">
+        <v>45</v>
+      </c>
+      <c r="M47">
+        <v>17030</v>
+      </c>
+      <c r="N47">
+        <v>12906</v>
+      </c>
+      <c r="O47">
+        <v>3649</v>
+      </c>
+      <c r="P47">
+        <v>32254</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Número de cesáreas anteriores</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ignorado</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Número de cesáreas anteriores</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>3911</v>
+      </c>
+      <c r="D49">
+        <v>265</v>
+      </c>
+      <c r="E49">
+        <v>62</v>
+      </c>
+      <c r="F49">
+        <v>53</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>15</v>
+      </c>
+      <c r="J49">
+        <v>13</v>
+      </c>
+      <c r="K49">
+        <v>2</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>313</v>
+      </c>
+      <c r="N49">
+        <v>172</v>
+      </c>
+      <c r="O49">
+        <v>32</v>
+      </c>
+      <c r="P49">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Número de óbitos fetais/abortos</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>366049</v>
+      </c>
+      <c r="D51">
+        <v>42792</v>
+      </c>
+      <c r="E51">
+        <v>23292</v>
+      </c>
+      <c r="F51">
+        <v>20719</v>
+      </c>
+      <c r="G51">
+        <v>1873</v>
+      </c>
+      <c r="H51">
+        <v>700</v>
+      </c>
+      <c r="I51">
+        <v>7893</v>
+      </c>
+      <c r="J51">
+        <v>6779</v>
+      </c>
+      <c r="K51">
+        <v>775</v>
+      </c>
+      <c r="L51">
+        <v>339</v>
+      </c>
+      <c r="M51">
+        <v>129024</v>
+      </c>
+      <c r="N51">
+        <v>77748</v>
+      </c>
+      <c r="O51">
+        <v>20091</v>
+      </c>
+      <c r="P51">
+        <v>322886</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Número de óbitos fetais/abortos</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>80456</v>
+      </c>
+      <c r="D52">
+        <v>10885</v>
+      </c>
+      <c r="E52">
+        <v>6200</v>
+      </c>
+      <c r="F52">
+        <v>5520</v>
+      </c>
+      <c r="G52">
+        <v>475</v>
+      </c>
+      <c r="H52">
+        <v>205</v>
+      </c>
+      <c r="I52">
+        <v>2045</v>
+      </c>
+      <c r="J52">
+        <v>1729</v>
+      </c>
+      <c r="K52">
+        <v>217</v>
+      </c>
+      <c r="L52">
+        <v>99</v>
+      </c>
+      <c r="M52">
+        <v>30399</v>
+      </c>
+      <c r="N52">
+        <v>19243</v>
+      </c>
+      <c r="O52">
+        <v>4665</v>
+      </c>
+      <c r="P52">
+        <v>69490</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Número de óbitos fetais/abortos</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2 ou mais</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>22489</v>
+      </c>
+      <c r="D53">
+        <v>3771</v>
+      </c>
+      <c r="E53">
+        <v>2247</v>
+      </c>
+      <c r="F53">
+        <v>1955</v>
+      </c>
+      <c r="G53">
+        <v>206</v>
+      </c>
+      <c r="H53">
+        <v>86</v>
+      </c>
+      <c r="I53">
+        <v>717</v>
+      </c>
+      <c r="J53">
+        <v>596</v>
+      </c>
+      <c r="K53">
+        <v>83</v>
+      </c>
+      <c r="L53">
+        <v>38</v>
+      </c>
+      <c r="M53">
+        <v>9216</v>
+      </c>
+      <c r="N53">
+        <v>6088</v>
+      </c>
+      <c r="O53">
+        <v>1442</v>
+      </c>
+      <c r="P53">
+        <v>18692</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Número de óbitos fetais/abortos</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ignorado</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>6</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>2</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Número de óbitos fetais/abortos</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>1627</v>
+      </c>
+      <c r="D55">
+        <v>236</v>
+      </c>
+      <c r="E55">
+        <v>125</v>
+      </c>
+      <c r="F55">
+        <v>105</v>
+      </c>
+      <c r="G55">
+        <v>16</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55">
+        <v>28</v>
+      </c>
+      <c r="J55">
+        <v>23</v>
+      </c>
+      <c r="K55">
+        <v>4</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>651</v>
+      </c>
+      <c r="N55">
+        <v>397</v>
+      </c>
+      <c r="O55">
+        <v>83</v>
+      </c>
+      <c r="P55">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Número de filhos vivos anteriores</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>211219</v>
+      </c>
+      <c r="D57">
+        <v>25718</v>
+      </c>
+      <c r="E57">
+        <v>14229</v>
+      </c>
+      <c r="F57">
+        <v>12455</v>
+      </c>
+      <c r="G57">
+        <v>1241</v>
+      </c>
+      <c r="H57">
+        <v>533</v>
+      </c>
+      <c r="I57">
+        <v>4950</v>
+      </c>
+      <c r="J57">
+        <v>4178</v>
+      </c>
+      <c r="K57">
+        <v>517</v>
+      </c>
+      <c r="L57">
+        <v>255</v>
+      </c>
+      <c r="M57">
+        <v>71860</v>
+      </c>
+      <c r="N57">
+        <v>45232</v>
+      </c>
+      <c r="O57">
+        <v>11968</v>
+      </c>
+      <c r="P57">
+        <v>185341</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Número de filhos vivos anteriores</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>149053</v>
+      </c>
+      <c r="D58">
+        <v>16439</v>
+      </c>
+      <c r="E58">
+        <v>9109</v>
+      </c>
+      <c r="F58">
+        <v>8183</v>
+      </c>
+      <c r="G58">
+        <v>692</v>
+      </c>
+      <c r="H58">
+        <v>234</v>
+      </c>
+      <c r="I58">
+        <v>3029</v>
+      </c>
+      <c r="J58">
+        <v>2640</v>
+      </c>
+      <c r="K58">
+        <v>276</v>
+      </c>
+      <c r="L58">
+        <v>113</v>
+      </c>
+      <c r="M58">
+        <v>55581</v>
+      </c>
+      <c r="N58">
+        <v>33594</v>
+      </c>
+      <c r="O58">
+        <v>8617</v>
+      </c>
+      <c r="P58">
+        <v>132463</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Número de filhos vivos anteriores</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2 ou mais</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>109310</v>
+      </c>
+      <c r="D59">
+        <v>15380</v>
+      </c>
+      <c r="E59">
+        <v>8439</v>
+      </c>
+      <c r="F59">
+        <v>7587</v>
+      </c>
+      <c r="G59">
+        <v>628</v>
+      </c>
+      <c r="H59">
+        <v>224</v>
+      </c>
+      <c r="I59">
+        <v>2685</v>
+      </c>
+      <c r="J59">
+        <v>2293</v>
+      </c>
+      <c r="K59">
+        <v>283</v>
+      </c>
+      <c r="L59">
+        <v>109</v>
+      </c>
+      <c r="M59">
+        <v>41458</v>
+      </c>
+      <c r="N59">
+        <v>24407</v>
+      </c>
+      <c r="O59">
+        <v>5639</v>
+      </c>
+      <c r="P59">
+        <v>93743</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Número de filhos vivos anteriores</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ignorado</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Número de filhos vivos anteriores</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>1041</v>
+      </c>
+      <c r="D61">
+        <v>147</v>
+      </c>
+      <c r="E61">
+        <v>87</v>
+      </c>
+      <c r="F61">
+        <v>74</v>
+      </c>
+      <c r="G61">
+        <v>9</v>
+      </c>
+      <c r="H61">
+        <v>4</v>
+      </c>
+      <c r="I61">
+        <v>19</v>
+      </c>
+      <c r="J61">
+        <v>16</v>
+      </c>
+      <c r="K61">
+        <v>3</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>392</v>
+      </c>
+      <c r="N61">
+        <v>243</v>
+      </c>
+      <c r="O61">
+        <v>58</v>
+      </c>
+      <c r="P61">
+        <v>871</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q61"/>
